--- a/data.mn/public/datasets/mongolbank-exchange-rates-monthly-major.xlsx
+++ b/data.mn/public/datasets/mongolbank-exchange-rates-monthly-major.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,249 +414,2053 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>currency_code</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>currency_name</t>
-        </is>
-      </c>
-      <c r="C1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I1" t="n">
-        <v>2026</v>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Chinese Yuan</t>
-        </is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>396.2248</v>
       </c>
       <c r="C2" t="n">
-        <v>407.919</v>
+        <v>3047.7123</v>
       </c>
       <c r="D2" t="n">
-        <v>441.6837</v>
+        <v>25.1074</v>
       </c>
       <c r="E2" t="n">
-        <v>466.3543</v>
+        <v>2.3529</v>
       </c>
       <c r="F2" t="n">
-        <v>489.7654</v>
+        <v>44.3581</v>
       </c>
       <c r="G2" t="n">
-        <v>471.0917</v>
-      </c>
-      <c r="H2" t="n">
-        <v>493.1622</v>
-      </c>
-      <c r="I2" t="n">
-        <v>522.8231</v>
+        <v>2743.5974</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Euro</t>
-        </is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>394.1017</v>
       </c>
       <c r="C3" t="n">
-        <v>3211.3764</v>
+        <v>3007.9597</v>
       </c>
       <c r="D3" t="n">
-        <v>3372.1588</v>
+        <v>25.0441</v>
       </c>
       <c r="E3" t="n">
-        <v>3302.2258</v>
+        <v>2.3083</v>
       </c>
       <c r="F3" t="n">
-        <v>3746.9359</v>
+        <v>43.0979</v>
       </c>
       <c r="G3" t="n">
-        <v>3667.5474</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4006.7397</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4157.0142</v>
+        <v>2756.9483</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JPY</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Japanese Yen</t>
-        </is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>394.57</v>
       </c>
       <c r="C4" t="n">
-        <v>26.3662</v>
+        <v>3065.8129</v>
       </c>
       <c r="D4" t="n">
-        <v>25.9688</v>
+        <v>25.7558</v>
       </c>
       <c r="E4" t="n">
-        <v>23.963</v>
+        <v>2.2735</v>
       </c>
       <c r="F4" t="n">
-        <v>24.7316</v>
+        <v>37.5961</v>
       </c>
       <c r="G4" t="n">
-        <v>22.4052</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.7133</v>
-      </c>
-      <c r="I4" t="n">
-        <v>22.5261</v>
+        <v>2768.9529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>South Korean Won</t>
-        </is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>393.469</v>
       </c>
       <c r="C5" t="n">
-        <v>2.388</v>
+        <v>3021.5643</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4913</v>
+        <v>25.8043</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4328</v>
+        <v>2.277</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6531</v>
+        <v>37.0893</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4869</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.4951</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.4252</v>
+        <v>2783.048</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Russian Ruble</t>
-        </is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>393.6887</v>
       </c>
       <c r="C6" t="n">
-        <v>39.1168</v>
+        <v>3050.5229</v>
       </c>
       <c r="D6" t="n">
-        <v>38.6907</v>
+        <v>26.1119</v>
       </c>
       <c r="E6" t="n">
-        <v>47.2247</v>
+        <v>2.2748</v>
       </c>
       <c r="F6" t="n">
-        <v>41.1573</v>
+        <v>38.3706</v>
       </c>
       <c r="G6" t="n">
-        <v>36.6804</v>
-      </c>
-      <c r="H6" t="n">
-        <v>42.6125</v>
-      </c>
-      <c r="I6" t="n">
-        <v>46.2154</v>
+        <v>2797.1452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>US Dollar</t>
-        </is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>397.2737</v>
       </c>
       <c r="C7" t="n">
-        <v>2813.0686</v>
+        <v>3167.0623</v>
       </c>
       <c r="D7" t="n">
-        <v>2849.2562</v>
+        <v>26.1753</v>
       </c>
       <c r="E7" t="n">
-        <v>3139.795</v>
+        <v>2.3287</v>
       </c>
       <c r="F7" t="n">
-        <v>3465.851</v>
+        <v>40.6117</v>
       </c>
       <c r="G7" t="n">
-        <v>3390.0289</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3544.864</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3574.939</v>
+        <v>2815.654</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>404.1861</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3240.3806</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26.5584</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.3645</v>
+      </c>
+      <c r="F8" t="n">
+        <v>39.6987</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2835.3158</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>411.0848</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3371.3871</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26.8987</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38.5897</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2848.9248</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>418.9777</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3366.7413</v>
+      </c>
+      <c r="D10" t="n">
+        <v>27.037</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.4247</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37.657</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2854.134</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>424.3942</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3357.5384</v>
+      </c>
+      <c r="D11" t="n">
+        <v>27.1265</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.4945</v>
+      </c>
+      <c r="F11" t="n">
+        <v>36.7726</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2853.6135</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>431.283</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3371.8713</v>
+      </c>
+      <c r="D12" t="n">
+        <v>27.3157</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.5533</v>
+      </c>
+      <c r="F12" t="n">
+        <v>37.0607</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2849.9577</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>435.7748</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3467.9632</v>
+      </c>
+      <c r="D13" t="n">
+        <v>27.4587</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.6039</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38.4994</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2849.5319</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>440.1106</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3471.6013</v>
+      </c>
+      <c r="D14" t="n">
+        <v>27.4745</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.5923</v>
+      </c>
+      <c r="F14" t="n">
+        <v>38.2826</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2849.8319</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>441.0564</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3446.5221</v>
+      </c>
+      <c r="D15" t="n">
+        <v>27.0514</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.5632</v>
+      </c>
+      <c r="F15" t="n">
+        <v>38.3571</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2849.6696</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>437.9197</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3392.5665</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26.2106</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.5197</v>
+      </c>
+      <c r="F16" t="n">
+        <v>38.2865</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2849.6226</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>436.7887</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3405.8023</v>
+      </c>
+      <c r="D17" t="n">
+        <v>26.1177</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.5487</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37.468</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2849.9003</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>442.9961</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3460.2477</v>
+      </c>
+      <c r="D18" t="n">
+        <v>26.0987</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.5377</v>
+      </c>
+      <c r="F18" t="n">
+        <v>38.5094</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2849.539</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>443.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3433.0223</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25.8773</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="F19" t="n">
+        <v>39.2867</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2849.0763</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>439.6974</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3368.8848</v>
+      </c>
+      <c r="D20" t="n">
+        <v>25.8345</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.4855</v>
+      </c>
+      <c r="F20" t="n">
+        <v>38.5194</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2848.9435</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>439.8674</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3353.1923</v>
+      </c>
+      <c r="D21" t="n">
+        <v>25.9342</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.4529</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38.7071</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2848.8332</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>441.255</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3356.714</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25.8647</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.4317</v>
+      </c>
+      <c r="F22" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2848.861</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>443.6935</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3306.1668</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25.2045</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F23" t="n">
+        <v>39.8926</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2848.9039</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>445.882</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3250.8197</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24.9427</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.408</v>
+      </c>
+      <c r="F24" t="n">
+        <v>39.226</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2848.9933</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>447.3381</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3220.3652</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.0152</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.4058</v>
+      </c>
+      <c r="F25" t="n">
+        <v>38.6535</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2848.8997</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>448.231</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3224.7781</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24.8032</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.3813</v>
+      </c>
+      <c r="F26" t="n">
+        <v>37.3329</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2849.4216</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>450.3032</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3234.3221</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24.7843</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.3843</v>
+      </c>
+      <c r="F27" t="n">
+        <v>36.5725</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2856.5871</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>457.1132</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3195.7703</v>
+      </c>
+      <c r="D28" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.3755</v>
+      </c>
+      <c r="F28" t="n">
+        <v>27.4961</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2900.0323</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>473.1897</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3291.9273</v>
+      </c>
+      <c r="D29" t="n">
+        <v>24.0907</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.4623</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38.175</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3039.089</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>464.1629</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3287.3013</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24.1445</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.4532</v>
+      </c>
+      <c r="F30" t="n">
+        <v>48.2252</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3110.1326</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>466.847</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3306.1627</v>
+      </c>
+      <c r="D31" t="n">
+        <v>23.3873</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.4457</v>
+      </c>
+      <c r="F31" t="n">
+        <v>54.868</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3123.6937</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>468.6465</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3216.5855</v>
+      </c>
+      <c r="D32" t="n">
+        <v>23.1729</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.4174</v>
+      </c>
+      <c r="F32" t="n">
+        <v>53.7281</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3151.72</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>468.6519</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3228.5926</v>
+      </c>
+      <c r="D33" t="n">
+        <v>23.5823</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.4145</v>
+      </c>
+      <c r="F33" t="n">
+        <v>52.6658</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3186.091</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>463.872</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3227.6343</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22.776</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.3343</v>
+      </c>
+      <c r="F34" t="n">
+        <v>54.3737</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3252.7293</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>468.6758</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3313.7181</v>
+      </c>
+      <c r="D35" t="n">
+        <v>22.921</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F35" t="n">
+        <v>54.9648</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3369.2642</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>474.916</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3472.7517</v>
+      </c>
+      <c r="D36" t="n">
+        <v>23.9497</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.5123</v>
+      </c>
+      <c r="F36" t="n">
+        <v>55.9687</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3406.9767</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>491.6419</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3627.1661</v>
+      </c>
+      <c r="D37" t="n">
+        <v>25.4535</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.6526</v>
+      </c>
+      <c r="F37" t="n">
+        <v>52.3261</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3431.8026</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>510.1913</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3734.13</v>
+      </c>
+      <c r="D38" t="n">
+        <v>26.5839</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.7845</v>
+      </c>
+      <c r="F38" t="n">
+        <v>49.8345</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3467.0823</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>513.4657</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3763.1971</v>
+      </c>
+      <c r="D39" t="n">
+        <v>26.4825</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.7518</v>
+      </c>
+      <c r="F39" t="n">
+        <v>48.0339</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3509.3257</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>511.3174</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3774.8019</v>
+      </c>
+      <c r="D40" t="n">
+        <v>26.3619</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.7029</v>
+      </c>
+      <c r="F40" t="n">
+        <v>46.3087</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3525.2723</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>507.8647</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3834.0547</v>
+      </c>
+      <c r="D41" t="n">
+        <v>26.2163</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.6473</v>
+      </c>
+      <c r="F41" t="n">
+        <v>43.1463</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3496.8107</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>495.4732</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3762.3958</v>
+      </c>
+      <c r="D42" t="n">
+        <v>25.2797</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.6058</v>
+      </c>
+      <c r="F42" t="n">
+        <v>43.8487</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3461.0739</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>480.7877</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3726.0277</v>
+      </c>
+      <c r="D43" t="n">
+        <v>24.3657</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.651</v>
+      </c>
+      <c r="F43" t="n">
+        <v>41.2537</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3439.0003</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>477.4035</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3780.0929</v>
+      </c>
+      <c r="D44" t="n">
+        <v>24.2187</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.6619</v>
+      </c>
+      <c r="F44" t="n">
+        <v>37.8665</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3441.1329</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>478.5442</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3785.2481</v>
+      </c>
+      <c r="D45" t="n">
+        <v>23.9823</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.6229</v>
+      </c>
+      <c r="F45" t="n">
+        <v>36.4048</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3470.0952</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>475.0297</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3705.9457</v>
+      </c>
+      <c r="D46" t="n">
+        <v>23.4877</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.5993</v>
+      </c>
+      <c r="F46" t="n">
+        <v>35.863</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3466.2827</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>472.3765</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3646.58</v>
+      </c>
+      <c r="D47" t="n">
+        <v>23.0819</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.5548</v>
+      </c>
+      <c r="F47" t="n">
+        <v>35.6248</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3452.5713</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>475.661</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3712.935</v>
+      </c>
+      <c r="D48" t="n">
+        <v>22.9373</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="F48" t="n">
+        <v>38.0587</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3440.8883</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>479.07</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3737.8223</v>
+      </c>
+      <c r="D49" t="n">
+        <v>23.7813</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.6261</v>
+      </c>
+      <c r="F49" t="n">
+        <v>37.6445</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3420.6768</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>475.2116</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3718.2419</v>
+      </c>
+      <c r="D50" t="n">
+        <v>23.3387</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.5729</v>
+      </c>
+      <c r="F50" t="n">
+        <v>38.1461</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3407.4471</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>471.6493</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3663.771</v>
+      </c>
+      <c r="D51" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.5483</v>
+      </c>
+      <c r="F51" t="n">
+        <v>37.031</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3392.4545</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>468.6177</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3665.5181</v>
+      </c>
+      <c r="D52" t="n">
+        <v>22.5313</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.5306</v>
+      </c>
+      <c r="F52" t="n">
+        <v>36.8155</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3376.2123</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>466.4317</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3623.003</v>
+      </c>
+      <c r="D53" t="n">
+        <v>21.9647</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.4663</v>
+      </c>
+      <c r="F53" t="n">
+        <v>36.304</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3376.5297</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>467.4119</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3652.9274</v>
+      </c>
+      <c r="D54" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.4765</v>
+      </c>
+      <c r="F54" t="n">
+        <v>37.1797</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3381.2929</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>466.036</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3638.4013</v>
+      </c>
+      <c r="D55" t="n">
+        <v>21.415</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.4483</v>
+      </c>
+      <c r="F55" t="n">
+        <v>38.467</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3381.1577</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>465.441</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3663.7397</v>
+      </c>
+      <c r="D56" t="n">
+        <v>21.3994</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.4439</v>
+      </c>
+      <c r="F56" t="n">
+        <v>38.7758</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3380.89</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>472.4629</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3719.9181</v>
+      </c>
+      <c r="D57" t="n">
+        <v>23.0552</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>37.9381</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3381.0106</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>477.9393</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3755.7013</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23.6343</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.5417</v>
+      </c>
+      <c r="F58" t="n">
+        <v>37.0077</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3380.9967</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>478.6542</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3698.7581</v>
+      </c>
+      <c r="D59" t="n">
+        <v>22.6865</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.4923</v>
+      </c>
+      <c r="F59" t="n">
+        <v>35.1987</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3391.6065</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>473.7953</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3630.862</v>
+      </c>
+      <c r="D60" t="n">
+        <v>22.207</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.448</v>
+      </c>
+      <c r="F60" t="n">
+        <v>33.9667</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3412.7827</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>469.45</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3579.7265</v>
+      </c>
+      <c r="D61" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.3739</v>
+      </c>
+      <c r="F61" t="n">
+        <v>33.3345</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3417.9658</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>469.6735</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3548.9319</v>
+      </c>
+      <c r="D62" t="n">
+        <v>21.9084</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.3594</v>
+      </c>
+      <c r="F62" t="n">
+        <v>33.4574</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3430.6061</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>475.5232</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3603.1025</v>
+      </c>
+      <c r="D63" t="n">
+        <v>22.7404</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.3932</v>
+      </c>
+      <c r="F63" t="n">
+        <v>37.4318</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3458.3239</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>478.9913</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3740.4994</v>
+      </c>
+      <c r="D64" t="n">
+        <v>23.2784</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.3835</v>
+      </c>
+      <c r="F64" t="n">
+        <v>40.479</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3474.0745</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>485.224</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3982.9473</v>
+      </c>
+      <c r="D65" t="n">
+        <v>24.5943</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="F65" t="n">
+        <v>42.5663</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3542.0263</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>494.9577</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4031.6529</v>
+      </c>
+      <c r="D66" t="n">
+        <v>24.6997</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.5665</v>
+      </c>
+      <c r="F66" t="n">
+        <v>44.2416</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3572.7958</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>498.119</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4120.4387</v>
+      </c>
+      <c r="D67" t="n">
+        <v>24.7723</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.6213</v>
+      </c>
+      <c r="F67" t="n">
+        <v>45.4193</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3577.5573</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>499.6635</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4194.8358</v>
+      </c>
+      <c r="D68" t="n">
+        <v>24.4319</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.6035</v>
+      </c>
+      <c r="F68" t="n">
+        <v>45.4813</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3584.6771</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>500.6116</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4175.7932</v>
+      </c>
+      <c r="D69" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.5813</v>
+      </c>
+      <c r="F69" t="n">
+        <v>44.8645</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3592.1368</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>504.387</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4214.8923</v>
+      </c>
+      <c r="D70" t="n">
+        <v>24.281</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F70" t="n">
+        <v>43.336</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3593.9177</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>504.4494</v>
+      </c>
+      <c r="C71" t="n">
+        <v>4183.3048</v>
+      </c>
+      <c r="D71" t="n">
+        <v>23.7632</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.5239</v>
+      </c>
+      <c r="F71" t="n">
+        <v>44.3803</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3592.1813</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>502.344</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4127.2437</v>
+      </c>
+      <c r="D72" t="n">
+        <v>23.0107</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.4473</v>
+      </c>
+      <c r="F72" t="n">
+        <v>44.442</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3570.7323</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>504.0019</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4157.2342</v>
+      </c>
+      <c r="D73" t="n">
+        <v>22.7694</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="F73" t="n">
+        <v>45.251</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3549.3394</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>510.8061</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4176.3816</v>
+      </c>
+      <c r="D74" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.4439</v>
+      </c>
+      <c r="F74" t="n">
+        <v>45.6568</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3560.7381</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>515.9896</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4224.05</v>
+      </c>
+      <c r="D75" t="n">
+        <v>23.0339</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.4668</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.3564</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3565.7493</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>517.3329</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4123.7955</v>
+      </c>
+      <c r="D76" t="n">
+        <v>22.4958</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2.3965</v>
+      </c>
+      <c r="F76" t="n">
+        <v>44.2739</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3566.5984</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>522.422</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4175.4867</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22.4263</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2.4043</v>
+      </c>
+      <c r="F77" t="n">
+        <v>46.5207</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3573.5427</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>525.9168</v>
+      </c>
+      <c r="C78" t="n">
+        <v>4175.0023</v>
+      </c>
+      <c r="D78" t="n">
+        <v>22.6213</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.3987</v>
+      </c>
+      <c r="F78" t="n">
+        <v>48.9439</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3576.0874</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>527.876</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4118.6083</v>
+      </c>
+      <c r="D79" t="n">
+        <v>22.2557</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.336</v>
+      </c>
+      <c r="F79" t="n">
+        <v>48.476</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3576.686</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>528.6558</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4097.3174</v>
+      </c>
+      <c r="D80" t="n">
+        <v>22.0748</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.3942</v>
+      </c>
+      <c r="F80" t="n">
+        <v>46.3065</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3585.7745</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>533.5857999999999</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4165.4719</v>
+      </c>
+      <c r="D81" t="n">
+        <v>22.6113</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.561</v>
+      </c>
+      <c r="F81" t="n">
+        <v>43.1887</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3594.3355</v>
       </c>
     </row>
   </sheetData>
@@ -670,249 +2474,2053 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>валютын_код</t>
+          <t>огноо</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>валютын_нэр</t>
-        </is>
-      </c>
-      <c r="C1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="F1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H1" t="n">
-        <v>2025</v>
-      </c>
-      <c r="I1" t="n">
-        <v>2026</v>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Хятад юань</t>
-        </is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>396.2248</v>
       </c>
       <c r="C2" t="n">
-        <v>407.919</v>
+        <v>3047.7123</v>
       </c>
       <c r="D2" t="n">
-        <v>441.6837</v>
+        <v>25.1074</v>
       </c>
       <c r="E2" t="n">
-        <v>466.3543</v>
+        <v>2.3529</v>
       </c>
       <c r="F2" t="n">
-        <v>489.7654</v>
+        <v>44.3581</v>
       </c>
       <c r="G2" t="n">
-        <v>471.0917</v>
-      </c>
-      <c r="H2" t="n">
-        <v>493.1622</v>
-      </c>
-      <c r="I2" t="n">
-        <v>522.8231</v>
+        <v>2743.5974</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Евро</t>
-        </is>
+          <t>2020-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>394.1017</v>
       </c>
       <c r="C3" t="n">
-        <v>3211.3764</v>
+        <v>3007.9597</v>
       </c>
       <c r="D3" t="n">
-        <v>3372.1588</v>
+        <v>25.0441</v>
       </c>
       <c r="E3" t="n">
-        <v>3302.2258</v>
+        <v>2.3083</v>
       </c>
       <c r="F3" t="n">
-        <v>3746.9359</v>
+        <v>43.0979</v>
       </c>
       <c r="G3" t="n">
-        <v>3667.5474</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4006.7397</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4157.0142</v>
+        <v>2756.9483</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JPY</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Японы иен</t>
-        </is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>394.57</v>
       </c>
       <c r="C4" t="n">
-        <v>26.3662</v>
+        <v>3065.8129</v>
       </c>
       <c r="D4" t="n">
-        <v>25.9688</v>
+        <v>25.7558</v>
       </c>
       <c r="E4" t="n">
-        <v>23.963</v>
+        <v>2.2735</v>
       </c>
       <c r="F4" t="n">
-        <v>24.7316</v>
+        <v>37.5961</v>
       </c>
       <c r="G4" t="n">
-        <v>22.4052</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.7133</v>
-      </c>
-      <c r="I4" t="n">
-        <v>22.5261</v>
+        <v>2768.9529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Солонгосын вон</t>
-        </is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>393.469</v>
       </c>
       <c r="C5" t="n">
-        <v>2.388</v>
+        <v>3021.5643</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4913</v>
+        <v>25.8043</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4328</v>
+        <v>2.277</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6531</v>
+        <v>37.0893</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4869</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.4951</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.4252</v>
+        <v>2783.048</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RUB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Оросын рубль</t>
-        </is>
+          <t>2020-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>393.6887</v>
       </c>
       <c r="C6" t="n">
-        <v>39.1168</v>
+        <v>3050.5229</v>
       </c>
       <c r="D6" t="n">
-        <v>38.6907</v>
+        <v>26.1119</v>
       </c>
       <c r="E6" t="n">
-        <v>47.2247</v>
+        <v>2.2748</v>
       </c>
       <c r="F6" t="n">
-        <v>41.1573</v>
+        <v>38.3706</v>
       </c>
       <c r="G6" t="n">
-        <v>36.6804</v>
-      </c>
-      <c r="H6" t="n">
-        <v>42.6125</v>
-      </c>
-      <c r="I6" t="n">
-        <v>46.2154</v>
+        <v>2797.1452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Америк доллар</t>
-        </is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>397.2737</v>
       </c>
       <c r="C7" t="n">
-        <v>2813.0686</v>
+        <v>3167.0623</v>
       </c>
       <c r="D7" t="n">
-        <v>2849.2562</v>
+        <v>26.1753</v>
       </c>
       <c r="E7" t="n">
-        <v>3139.795</v>
+        <v>2.3287</v>
       </c>
       <c r="F7" t="n">
-        <v>3465.851</v>
+        <v>40.6117</v>
       </c>
       <c r="G7" t="n">
-        <v>3390.0289</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3544.864</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3574.939</v>
+        <v>2815.654</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>404.1861</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3240.3806</v>
+      </c>
+      <c r="D8" t="n">
+        <v>26.5584</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.3645</v>
+      </c>
+      <c r="F8" t="n">
+        <v>39.6987</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2835.3158</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>411.0848</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3371.3871</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26.8987</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>38.5897</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2848.9248</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020-09-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>418.9777</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3366.7413</v>
+      </c>
+      <c r="D10" t="n">
+        <v>27.037</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.4247</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37.657</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2854.134</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-10-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>424.3942</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3357.5384</v>
+      </c>
+      <c r="D11" t="n">
+        <v>27.1265</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.4945</v>
+      </c>
+      <c r="F11" t="n">
+        <v>36.7726</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2853.6135</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>431.283</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3371.8713</v>
+      </c>
+      <c r="D12" t="n">
+        <v>27.3157</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.5533</v>
+      </c>
+      <c r="F12" t="n">
+        <v>37.0607</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2849.9577</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>435.7748</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3467.9632</v>
+      </c>
+      <c r="D13" t="n">
+        <v>27.4587</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.6039</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38.4994</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2849.5319</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>440.1106</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3471.6013</v>
+      </c>
+      <c r="D14" t="n">
+        <v>27.4745</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.5923</v>
+      </c>
+      <c r="F14" t="n">
+        <v>38.2826</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2849.8319</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021-02-01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>441.0564</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3446.5221</v>
+      </c>
+      <c r="D15" t="n">
+        <v>27.0514</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.5632</v>
+      </c>
+      <c r="F15" t="n">
+        <v>38.3571</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2849.6696</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>437.9197</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3392.5665</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26.2106</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.5197</v>
+      </c>
+      <c r="F16" t="n">
+        <v>38.2865</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2849.6226</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>436.7887</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3405.8023</v>
+      </c>
+      <c r="D17" t="n">
+        <v>26.1177</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.5487</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37.468</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2849.9003</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-05-01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>442.9961</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3460.2477</v>
+      </c>
+      <c r="D18" t="n">
+        <v>26.0987</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.5377</v>
+      </c>
+      <c r="F18" t="n">
+        <v>38.5094</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2849.539</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>443.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3433.0223</v>
+      </c>
+      <c r="D19" t="n">
+        <v>25.8773</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="F19" t="n">
+        <v>39.2867</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2849.0763</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-07-01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>439.6974</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3368.8848</v>
+      </c>
+      <c r="D20" t="n">
+        <v>25.8345</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.4855</v>
+      </c>
+      <c r="F20" t="n">
+        <v>38.5194</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2848.9435</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>439.8674</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3353.1923</v>
+      </c>
+      <c r="D21" t="n">
+        <v>25.9342</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.4529</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38.7071</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2848.8332</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>441.255</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3356.714</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25.8647</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.4317</v>
+      </c>
+      <c r="F22" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2848.861</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>443.6935</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3306.1668</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25.2045</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F23" t="n">
+        <v>39.8926</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2848.9039</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>445.882</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3250.8197</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24.9427</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.408</v>
+      </c>
+      <c r="F24" t="n">
+        <v>39.226</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2848.9933</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>447.3381</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3220.3652</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25.0152</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.4058</v>
+      </c>
+      <c r="F25" t="n">
+        <v>38.6535</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2848.8997</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>448.231</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3224.7781</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24.8032</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.3813</v>
+      </c>
+      <c r="F26" t="n">
+        <v>37.3329</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2849.4216</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>450.3032</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3234.3221</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24.7843</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.3843</v>
+      </c>
+      <c r="F27" t="n">
+        <v>36.5725</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2856.5871</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>457.1132</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3195.7703</v>
+      </c>
+      <c r="D28" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.3755</v>
+      </c>
+      <c r="F28" t="n">
+        <v>27.4961</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2900.0323</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>473.1897</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3291.9273</v>
+      </c>
+      <c r="D29" t="n">
+        <v>24.0907</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.4623</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38.175</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3039.089</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>464.1629</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3287.3013</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24.1445</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.4532</v>
+      </c>
+      <c r="F30" t="n">
+        <v>48.2252</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3110.1326</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>466.847</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3306.1627</v>
+      </c>
+      <c r="D31" t="n">
+        <v>23.3873</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.4457</v>
+      </c>
+      <c r="F31" t="n">
+        <v>54.868</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3123.6937</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>468.6465</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3216.5855</v>
+      </c>
+      <c r="D32" t="n">
+        <v>23.1729</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.4174</v>
+      </c>
+      <c r="F32" t="n">
+        <v>53.7281</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3151.72</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>468.6519</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3228.5926</v>
+      </c>
+      <c r="D33" t="n">
+        <v>23.5823</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.4145</v>
+      </c>
+      <c r="F33" t="n">
+        <v>52.6658</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3186.091</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>463.872</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3227.6343</v>
+      </c>
+      <c r="D34" t="n">
+        <v>22.776</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.3343</v>
+      </c>
+      <c r="F34" t="n">
+        <v>54.3737</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3252.7293</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>468.6758</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3313.7181</v>
+      </c>
+      <c r="D35" t="n">
+        <v>22.921</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F35" t="n">
+        <v>54.9648</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3369.2642</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>474.916</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3472.7517</v>
+      </c>
+      <c r="D36" t="n">
+        <v>23.9497</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.5123</v>
+      </c>
+      <c r="F36" t="n">
+        <v>55.9687</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3406.9767</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>491.6419</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3627.1661</v>
+      </c>
+      <c r="D37" t="n">
+        <v>25.4535</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.6526</v>
+      </c>
+      <c r="F37" t="n">
+        <v>52.3261</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3431.8026</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>510.1913</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3734.13</v>
+      </c>
+      <c r="D38" t="n">
+        <v>26.5839</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.7845</v>
+      </c>
+      <c r="F38" t="n">
+        <v>49.8345</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3467.0823</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>513.4657</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3763.1971</v>
+      </c>
+      <c r="D39" t="n">
+        <v>26.4825</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.7518</v>
+      </c>
+      <c r="F39" t="n">
+        <v>48.0339</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3509.3257</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>511.3174</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3774.8019</v>
+      </c>
+      <c r="D40" t="n">
+        <v>26.3619</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.7029</v>
+      </c>
+      <c r="F40" t="n">
+        <v>46.3087</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3525.2723</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>507.8647</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3834.0547</v>
+      </c>
+      <c r="D41" t="n">
+        <v>26.2163</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.6473</v>
+      </c>
+      <c r="F41" t="n">
+        <v>43.1463</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3496.8107</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>495.4732</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3762.3958</v>
+      </c>
+      <c r="D42" t="n">
+        <v>25.2797</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.6058</v>
+      </c>
+      <c r="F42" t="n">
+        <v>43.8487</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3461.0739</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>480.7877</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3726.0277</v>
+      </c>
+      <c r="D43" t="n">
+        <v>24.3657</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.651</v>
+      </c>
+      <c r="F43" t="n">
+        <v>41.2537</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3439.0003</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>477.4035</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3780.0929</v>
+      </c>
+      <c r="D44" t="n">
+        <v>24.2187</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.6619</v>
+      </c>
+      <c r="F44" t="n">
+        <v>37.8665</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3441.1329</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>478.5442</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3785.2481</v>
+      </c>
+      <c r="D45" t="n">
+        <v>23.9823</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.6229</v>
+      </c>
+      <c r="F45" t="n">
+        <v>36.4048</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3470.0952</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>475.0297</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3705.9457</v>
+      </c>
+      <c r="D46" t="n">
+        <v>23.4877</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.5993</v>
+      </c>
+      <c r="F46" t="n">
+        <v>35.863</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3466.2827</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>472.3765</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3646.58</v>
+      </c>
+      <c r="D47" t="n">
+        <v>23.0819</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.5548</v>
+      </c>
+      <c r="F47" t="n">
+        <v>35.6248</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3452.5713</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>475.661</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3712.935</v>
+      </c>
+      <c r="D48" t="n">
+        <v>22.9373</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="F48" t="n">
+        <v>38.0587</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3440.8883</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>479.07</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3737.8223</v>
+      </c>
+      <c r="D49" t="n">
+        <v>23.7813</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.6261</v>
+      </c>
+      <c r="F49" t="n">
+        <v>37.6445</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3420.6768</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>475.2116</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3718.2419</v>
+      </c>
+      <c r="D50" t="n">
+        <v>23.3387</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.5729</v>
+      </c>
+      <c r="F50" t="n">
+        <v>38.1461</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3407.4471</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>471.6493</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3663.771</v>
+      </c>
+      <c r="D51" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.5483</v>
+      </c>
+      <c r="F51" t="n">
+        <v>37.031</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3392.4545</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>468.6177</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3665.5181</v>
+      </c>
+      <c r="D52" t="n">
+        <v>22.5313</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.5306</v>
+      </c>
+      <c r="F52" t="n">
+        <v>36.8155</v>
+      </c>
+      <c r="G52" t="n">
+        <v>3376.2123</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>466.4317</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3623.003</v>
+      </c>
+      <c r="D53" t="n">
+        <v>21.9647</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.4663</v>
+      </c>
+      <c r="F53" t="n">
+        <v>36.304</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3376.5297</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>467.4119</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3652.9274</v>
+      </c>
+      <c r="D54" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.4765</v>
+      </c>
+      <c r="F54" t="n">
+        <v>37.1797</v>
+      </c>
+      <c r="G54" t="n">
+        <v>3381.2929</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>466.036</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3638.4013</v>
+      </c>
+      <c r="D55" t="n">
+        <v>21.415</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.4483</v>
+      </c>
+      <c r="F55" t="n">
+        <v>38.467</v>
+      </c>
+      <c r="G55" t="n">
+        <v>3381.1577</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>465.441</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3663.7397</v>
+      </c>
+      <c r="D56" t="n">
+        <v>21.3994</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.4439</v>
+      </c>
+      <c r="F56" t="n">
+        <v>38.7758</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3380.89</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>472.4629</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3719.9181</v>
+      </c>
+      <c r="D57" t="n">
+        <v>23.0552</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>37.9381</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3381.0106</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>477.9393</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3755.7013</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23.6343</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2.5417</v>
+      </c>
+      <c r="F58" t="n">
+        <v>37.0077</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3380.9967</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>478.6542</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3698.7581</v>
+      </c>
+      <c r="D59" t="n">
+        <v>22.6865</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.4923</v>
+      </c>
+      <c r="F59" t="n">
+        <v>35.1987</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3391.6065</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>473.7953</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3630.862</v>
+      </c>
+      <c r="D60" t="n">
+        <v>22.207</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.448</v>
+      </c>
+      <c r="F60" t="n">
+        <v>33.9667</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3412.7827</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>469.45</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3579.7265</v>
+      </c>
+      <c r="D61" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.3739</v>
+      </c>
+      <c r="F61" t="n">
+        <v>33.3345</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3417.9658</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>469.6735</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3548.9319</v>
+      </c>
+      <c r="D62" t="n">
+        <v>21.9084</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.3594</v>
+      </c>
+      <c r="F62" t="n">
+        <v>33.4574</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3430.6061</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>475.5232</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3603.1025</v>
+      </c>
+      <c r="D63" t="n">
+        <v>22.7404</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.3932</v>
+      </c>
+      <c r="F63" t="n">
+        <v>37.4318</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3458.3239</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>478.9913</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3740.4994</v>
+      </c>
+      <c r="D64" t="n">
+        <v>23.2784</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2.3835</v>
+      </c>
+      <c r="F64" t="n">
+        <v>40.479</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3474.0745</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>485.224</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3982.9473</v>
+      </c>
+      <c r="D65" t="n">
+        <v>24.5943</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="F65" t="n">
+        <v>42.5663</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3542.0263</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>494.9577</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4031.6529</v>
+      </c>
+      <c r="D66" t="n">
+        <v>24.6997</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2.5665</v>
+      </c>
+      <c r="F66" t="n">
+        <v>44.2416</v>
+      </c>
+      <c r="G66" t="n">
+        <v>3572.7958</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>498.119</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4120.4387</v>
+      </c>
+      <c r="D67" t="n">
+        <v>24.7723</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.6213</v>
+      </c>
+      <c r="F67" t="n">
+        <v>45.4193</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3577.5573</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>499.6635</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4194.8358</v>
+      </c>
+      <c r="D68" t="n">
+        <v>24.4319</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2.6035</v>
+      </c>
+      <c r="F68" t="n">
+        <v>45.4813</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3584.6771</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>500.6116</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4175.7932</v>
+      </c>
+      <c r="D69" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.5813</v>
+      </c>
+      <c r="F69" t="n">
+        <v>44.8645</v>
+      </c>
+      <c r="G69" t="n">
+        <v>3592.1368</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>504.387</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4214.8923</v>
+      </c>
+      <c r="D70" t="n">
+        <v>24.281</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F70" t="n">
+        <v>43.336</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3593.9177</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>504.4494</v>
+      </c>
+      <c r="C71" t="n">
+        <v>4183.3048</v>
+      </c>
+      <c r="D71" t="n">
+        <v>23.7632</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.5239</v>
+      </c>
+      <c r="F71" t="n">
+        <v>44.3803</v>
+      </c>
+      <c r="G71" t="n">
+        <v>3592.1813</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>502.344</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4127.2437</v>
+      </c>
+      <c r="D72" t="n">
+        <v>23.0107</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.4473</v>
+      </c>
+      <c r="F72" t="n">
+        <v>44.442</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3570.7323</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>504.0019</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4157.2342</v>
+      </c>
+      <c r="D73" t="n">
+        <v>22.7694</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="F73" t="n">
+        <v>45.251</v>
+      </c>
+      <c r="G73" t="n">
+        <v>3549.3394</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>510.8061</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4176.3816</v>
+      </c>
+      <c r="D74" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.4439</v>
+      </c>
+      <c r="F74" t="n">
+        <v>45.6568</v>
+      </c>
+      <c r="G74" t="n">
+        <v>3560.7381</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>515.9896</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4224.05</v>
+      </c>
+      <c r="D75" t="n">
+        <v>23.0339</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.4668</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.3564</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3565.7493</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>517.3329</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4123.7955</v>
+      </c>
+      <c r="D76" t="n">
+        <v>22.4958</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2.3965</v>
+      </c>
+      <c r="F76" t="n">
+        <v>44.2739</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3566.5984</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>522.422</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4175.4867</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22.4263</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2.4043</v>
+      </c>
+      <c r="F77" t="n">
+        <v>46.5207</v>
+      </c>
+      <c r="G77" t="n">
+        <v>3573.5427</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>525.9168</v>
+      </c>
+      <c r="C78" t="n">
+        <v>4175.0023</v>
+      </c>
+      <c r="D78" t="n">
+        <v>22.6213</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.3987</v>
+      </c>
+      <c r="F78" t="n">
+        <v>48.9439</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3576.0874</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>527.876</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4118.6083</v>
+      </c>
+      <c r="D79" t="n">
+        <v>22.2557</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.336</v>
+      </c>
+      <c r="F79" t="n">
+        <v>48.476</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3576.686</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>528.6558</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4097.3174</v>
+      </c>
+      <c r="D80" t="n">
+        <v>22.0748</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2.3942</v>
+      </c>
+      <c r="F80" t="n">
+        <v>46.3065</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3585.7745</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>533.5857999999999</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4165.4719</v>
+      </c>
+      <c r="D81" t="n">
+        <v>22.6113</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.561</v>
+      </c>
+      <c r="F81" t="n">
+        <v>43.1887</v>
+      </c>
+      <c r="G81" t="n">
+        <v>3594.3355</v>
       </c>
     </row>
   </sheetData>

--- a/data.mn/public/datasets/mongolbank-exchange-rates-monthly-major.xlsx
+++ b/data.mn/public/datasets/mongolbank-exchange-rates-monthly-major.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2463,6 +2463,31 @@
         <v>3594.3355</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>535.936</v>
+      </c>
+      <c r="C82" t="n">
+        <v>4141.153</v>
+      </c>
+      <c r="D82" t="n">
+        <v>22.9837</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.6457</v>
+      </c>
+      <c r="F82" t="n">
+        <v>42.3143</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3595.4853</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2474,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4523,6 +4548,31 @@
         <v>3594.3355</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>535.936</v>
+      </c>
+      <c r="C82" t="n">
+        <v>4141.153</v>
+      </c>
+      <c r="D82" t="n">
+        <v>22.9837</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.6457</v>
+      </c>
+      <c r="F82" t="n">
+        <v>42.3143</v>
+      </c>
+      <c r="G82" t="n">
+        <v>3595.4853</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
